--- a/naver-place-crawler/results_hair/종로_미용실.xlsx
+++ b/naver-place-crawler/results_hair/종로_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V299"/>
+  <dimension ref="A1:V352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22761,30 +22761,34 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>배관,냉난방공사</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>관통자들</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>야드</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>shorty_@naver.com</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>0504-1362-7714</t>
+          <t>0507-1420-8068</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭길 64</t>
+          <t>서울특별시 종로구 사직로8길 13-1</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bird.power/</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -22794,7 +22798,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -22815,17 +22819,17 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>2878</v>
       </c>
       <c r="Q243" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>3109</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -22834,12 +22838,12 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>2016678874</t>
+          <t>32618528</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2016678874</t>
+          <t>https://m.place.naver.com/place/32618528</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -22851,44 +22855,44 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>배관,냉난방공사</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>종로구싱크대막힘</t>
+          <t>수진박헤어살롱</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>ybreakiiu18@naver.com</t>
+          <t>hjstylemm@naver.com</t>
         </is>
       </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>0504-1362-6386</t>
+          <t>02-742-5364</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 동숭길 64</t>
+          <t>서울특별시 종로구 종로 209-1 2층</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://soojinparkhair.homebuilder.co.kr</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -22916,10 +22920,10 @@
         <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -22928,12 +22932,12 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>2094230357</t>
+          <t>1614206093</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094230357</t>
+          <t>https://m.place.naver.com/place/1614206093</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -22945,26 +22949,34 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>우성 이발관</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr"/>
+          <t>바르헤어 종로점</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>eogml944@naver.com</t>
+        </is>
+      </c>
       <c r="D245" t="inlineStr"/>
-      <c r="E245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0507-1361-3179</t>
+        </is>
+      </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 123-6</t>
+          <t>서울특별시 종로구 종로31길 43 루비온 오피스텔 102호 바르</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/eogml944</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -22974,12 +22986,12 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -22995,17 +23007,17 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>3326</v>
       </c>
       <c r="Q245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R245" t="n">
-        <v>0</v>
+        <v>3328</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -23014,12 +23026,12 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>1810176513</t>
+          <t>1284121704</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1810176513</t>
+          <t>https://m.place.naver.com/place/1284121704</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -23031,25 +23043,25 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>동신이발관</t>
+          <t>김훈미용실</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>02-2235-1753</t>
+          <t>02-739-5665</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로4길 37</t>
+          <t>서울특별시 종로구 통일로12길 27 1층</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -23089,13 +23101,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="Q246" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R246" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -23104,12 +23116,12 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>17984510</t>
+          <t>33481368</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17984510</t>
+          <t>https://m.place.naver.com/place/33481368</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -23121,34 +23133,34 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>마스터바버샵</t>
+          <t>준오헤어 스타필드애비뉴그랑서울점</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>charlesbarbershop_th@naver.com</t>
+          <t>juno_grand_seoul@naver.com</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>0507-1343-3926</t>
+          <t>0507-1399-6756</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 인사동5길 29 태화빌딩 지하1층 7호</t>
+          <t>서울특별시 종로구 종로 33 타워1 3층 준오헤어 스타필드애비뉴그랑서울점</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/charlesbarbershop_th</t>
+          <t>https://blog.naver.com/juno_grand_seoul</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -23179,17 +23191,17 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P247" t="n">
-        <v>1544</v>
+        <v>1907</v>
       </c>
       <c r="Q247" t="n">
-        <v>11</v>
+        <v>469</v>
       </c>
       <c r="R247" t="n">
-        <v>1555</v>
+        <v>2376</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -23198,12 +23210,12 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>17922754</t>
+          <t>2089192736</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17922754</t>
+          <t>https://m.place.naver.com/place/2089192736</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -23215,21 +23227,25 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>참존이발소</t>
+          <t>미소헤어</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>02-2263-4548</t>
+        </is>
+      </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로57길 8</t>
+          <t>서울특별시 종로구 종로32길 23-5</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -23269,13 +23285,13 @@
         </is>
       </c>
       <c r="P248" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>1</v>
-      </c>
       <c r="R248" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -23284,12 +23300,12 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>1358499310</t>
+          <t>37470772</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358499310</t>
+          <t>https://m.place.naver.com/place/37470772</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -23301,29 +23317,25 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>미일이발관</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>luvbittt@naver.com</t>
-        </is>
-      </c>
+          <t>르뱅헤어 한국프레스센터점</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>02-3673-5113</t>
+          <t>02-733-7922</t>
         </is>
       </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 낙산길 5</t>
+          <t>서울특별시 중구 세종대로 124 지하 1층</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -23363,13 +23375,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="Q249" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R249" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -23378,12 +23390,12 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>17967657</t>
+          <t>1054259249</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17967657</t>
+          <t>https://m.place.naver.com/place/1054259249</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -23395,30 +23407,30 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>클래씨바버샵 센터원점</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>rudqjasla@naver.com</t>
-        </is>
-      </c>
+          <t>수니미용실</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr"/>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>0507-1415-5411</t>
+        </is>
+      </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로5길 26 미래에셋센터원 지하1층 105호</t>
+          <t>서울특별시 종로구 삼일대로20길 19 2층(서광빌딩 201호)</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rudqjasla</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -23428,12 +23440,12 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -23449,17 +23461,17 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="Q250" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -23468,12 +23480,12 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>1061722057</t>
+          <t>2075149659</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061722057</t>
+          <t>https://m.place.naver.com/place/2075149659</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -23485,34 +23497,30 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>오클리먼33바버샵 을지로점</t>
+          <t>조치원 이발소</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>ocleremon33@gmail.com</t>
-        </is>
-      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>0507-1423-7334</t>
+          <t>02-9387-5427</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 170 을지트윈타워 B1층 115호</t>
+          <t>서울특별시 종로구 창덕궁길 33</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>https://youtube.com/ocleremon33</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -23522,7 +23530,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -23543,17 +23551,17 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P251" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="Q251" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -23562,12 +23570,12 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>2087530432</t>
+          <t>1823840809</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087530432</t>
+          <t>https://m.place.naver.com/place/1823840809</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -23579,25 +23587,25 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>청백이용원</t>
+          <t>축복이발관</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>02-2100-4674</t>
+          <t>0507-1426-9402</t>
         </is>
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 세종대로 209</t>
+          <t>서울특별시 종로구 난계로25길 84 2층 202호</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -23637,13 +23645,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q252" t="n">
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -23652,12 +23660,12 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>1967202167</t>
+          <t>1015090594</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1967202167</t>
+          <t>https://m.place.naver.com/place/1015090594</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -23669,29 +23677,29 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>협동이발소</t>
+          <t>복헤어</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>h22hyun@naver.com</t>
+          <t>dmsghks0809@naver.com</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0507-1338-2164</t>
+          <t>02-733-5861</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로54길 3 1층</t>
+          <t>서울특별시 종로구 옥인길 8 1층 복헤어</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -23731,13 +23739,13 @@
         </is>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="Q253" t="n">
         <v>1</v>
       </c>
       <c r="R253" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -23746,12 +23754,12 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>1149547002</t>
+          <t>35117481</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149547002</t>
+          <t>https://m.place.naver.com/place/35117481</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -23763,30 +23771,34 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>장수이용원</t>
+          <t>살롱존씨</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>j_jang_vely@naver.com</t>
+          <t>salonjohnc@naver.com</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0507-1394-2334</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로17길 36</t>
+          <t>서울특별시 종로구 종로14길 32 동흥빌딩 3층 302호</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/salonjohnc</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -23796,12 +23808,12 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -23817,17 +23829,17 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P254" t="n">
-        <v>1</v>
+        <v>558</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="R254" t="n">
-        <v>1</v>
+        <v>618</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -23836,12 +23848,12 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>20894646</t>
+          <t>1172080467</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20894646</t>
+          <t>https://m.place.naver.com/place/1172080467</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -23853,25 +23865,25 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>피카디리이용원</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>yeonju9195@naver.com</t>
-        </is>
-      </c>
+          <t>오헤어</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr"/>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>02-742-9701</t>
+        </is>
+      </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로5가길 33</t>
+          <t>서울특별시 종로구 성균관로 22-1</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -23911,13 +23923,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q255" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R255" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -23926,12 +23938,12 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>19418116</t>
+          <t>1566946941</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19418116</t>
+          <t>https://m.place.naver.com/place/1566946941</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -23943,34 +23955,26 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>마제스티바버샵 현대아울렛 동대문점</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>barber_kim@naver.com</t>
-        </is>
-      </c>
+          <t>사랑미용실</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>0507-1465-2628</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로13길 20 현대시티아울렛 6층</t>
+          <t>서울특별시 종로구 지봉로5길 7</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/barber_kim</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -23980,12 +23984,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -24005,13 +24009,13 @@
         </is>
       </c>
       <c r="P256" t="n">
-        <v>1081</v>
+        <v>1</v>
       </c>
       <c r="Q256" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>1159</v>
+        <v>1</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -24020,12 +24024,12 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>638147252</t>
+          <t>20913594</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/638147252</t>
+          <t>https://m.place.naver.com/place/20913594</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -24037,25 +24041,25 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>고호</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
+          <t>까망머리방</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>younggrg4398@naver.com</t>
+        </is>
+      </c>
       <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>02-737-2393</t>
-        </is>
-      </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 경희궁1길 32 신문로 하우스 1층 102호</t>
+          <t>서울특별시 종로구 옥인1길 2 까망머리방</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -24095,13 +24099,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>428</v>
+        <v>6</v>
       </c>
       <c r="Q257" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="R257" t="n">
-        <v>454</v>
+        <v>8</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -24110,12 +24114,12 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>1111299821</t>
+          <t>1013990105</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111299821</t>
+          <t>https://m.place.naver.com/place/1013990105</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -24127,34 +24131,34 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>클래씨바버샵 센트로폴리스점</t>
+          <t>르마오</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>rudqjasla@naver.com</t>
+          <t>togo-@naver.com</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>0507-1449-3128</t>
+          <t>0507-1395-8363</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 우정국로 26 1층 12호</t>
+          <t>서울특별시 종로구 자하문로10길 9-4 3층</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rudqjasla</t>
+          <t>https://www.instagram.com/lmao_hyuna</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -24169,7 +24173,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -24189,13 +24193,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>1000</v>
+        <v>351</v>
       </c>
       <c r="Q258" t="n">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="R258" t="n">
-        <v>1175</v>
+        <v>361</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -24204,12 +24208,12 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>1568475214</t>
+          <t>1355867821</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1568475214</t>
+          <t>https://m.place.naver.com/place/1355867821</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -24221,30 +24225,34 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>솔트 더 바버</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr"/>
+          <t>귀빈미용실</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>liujin81@naver.com</t>
+        </is>
+      </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>0507-1374-5695</t>
+          <t>02-379-3080</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 계동길 113 1층 1호</t>
+          <t>서울특별시 종로구 진흥로 484 귀빈미용실</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>https://instagram.com/salt_the_barber</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -24254,7 +24262,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -24275,17 +24283,17 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P259" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="Q259" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R259" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -24294,12 +24302,12 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
-          <t>1729274646</t>
+          <t>1990036314</t>
         </is>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1729274646</t>
+          <t>https://m.place.naver.com/place/1990036314</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
@@ -24311,34 +24319,26 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>바버샵 엉클부스 동대문점</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>barberizm@naver.com</t>
-        </is>
-      </c>
+          <t>비나헤어</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>02-6327-2727</t>
-        </is>
-      </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="inlineStr">
         <is>
-          <t>서울특별시 중구 장충단로 247 굿모닝시티 9층 바버샵 엉클부스</t>
+          <t>서울특별시 종로구 종로 335-5 덕용빌딩</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>http://unclebooth.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -24369,17 +24369,17 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P260" t="n">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="Q260" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>984</v>
+        <v>0</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -24388,12 +24388,12 @@
       </c>
       <c r="T260" t="inlineStr">
         <is>
-          <t>1284597205</t>
+          <t>2143385792</t>
         </is>
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1284597205</t>
+          <t>https://m.place.naver.com/place/2143385792</t>
         </is>
       </c>
       <c r="V260" t="inlineStr">
@@ -24405,34 +24405,34 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>이마이용원</t>
+          <t>이로헤어</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>ppassong@naver.com</t>
+          <t>irohair_@naver.com</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>02-730-9534</t>
+          <t>0507-1312-1501</t>
         </is>
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로1길 42</t>
+          <t>서울특별시 종로구 통일로12길 6-13 이로헤어</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/irohair_</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -24442,12 +24442,12 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -24467,13 +24467,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>21</v>
+        <v>1250</v>
       </c>
       <c r="Q261" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="R261" t="n">
-        <v>22</v>
+        <v>1343</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -24482,12 +24482,12 @@
       </c>
       <c r="T261" t="inlineStr">
         <is>
-          <t>1870076730</t>
+          <t>1790911315</t>
         </is>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870076730</t>
+          <t>https://m.place.naver.com/place/1790911315</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
@@ -24499,25 +24499,29 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>명성이발</t>
+          <t>준오헤어 대학로점</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>jsy34260@naver.com</t>
+          <t>haein3758@naver.com</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
-      <c r="E262" t="inlineStr"/>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>0507-1442-0610</t>
+        </is>
+      </c>
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 112</t>
+          <t>서울특별시 종로구 대학로 132 준오헤어 대학로점</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -24557,13 +24561,13 @@
         </is>
       </c>
       <c r="P262" t="n">
-        <v>1</v>
+        <v>16647</v>
       </c>
       <c r="Q262" t="n">
-        <v>1</v>
+        <v>294</v>
       </c>
       <c r="R262" t="n">
-        <v>2</v>
+        <v>16941</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -24572,12 +24576,12 @@
       </c>
       <c r="T262" t="inlineStr">
         <is>
-          <t>1188080296</t>
+          <t>37207298</t>
         </is>
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188080296</t>
+          <t>https://m.place.naver.com/place/37207298</t>
         </is>
       </c>
       <c r="V262" t="inlineStr">
@@ -24589,29 +24593,21 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>바버케이</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>dj_mok@naver.com</t>
-        </is>
-      </c>
+          <t>대원미용실</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>02-722-2823</t>
-        </is>
-      </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 20 경희궁파크팰리스 117호</t>
+          <t>서울특별시 종로구 종로 269-3</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -24651,13 +24647,13 @@
         </is>
       </c>
       <c r="P263" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="Q263" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="R263" t="n">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -24666,12 +24662,12 @@
       </c>
       <c r="T263" t="inlineStr">
         <is>
-          <t>1198195384</t>
+          <t>19406670</t>
         </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198195384</t>
+          <t>https://m.place.naver.com/place/19406670</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
@@ -24683,25 +24679,29 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>종묘이발관</t>
+          <t>박승철헤어스투디오 서대문역점</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>tisea007@naver.com</t>
+          <t>ssommya_da_@naver.com</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>0507-1402-5828</t>
+        </is>
+      </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 146</t>
+          <t>서울특별시 종로구 송월길 99 상가1층2152호</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -24741,13 +24741,13 @@
         </is>
       </c>
       <c r="P264" t="n">
-        <v>0</v>
+        <v>7651</v>
       </c>
       <c r="Q264" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R264" t="n">
-        <v>0</v>
+        <v>7682</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -24756,12 +24756,12 @@
       </c>
       <c r="T264" t="inlineStr">
         <is>
-          <t>1404095890</t>
+          <t>1122688407</t>
         </is>
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1404095890</t>
+          <t>https://m.place.naver.com/place/1122688407</t>
         </is>
       </c>
       <c r="V264" t="inlineStr">
@@ -24773,30 +24773,34 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>리얼리굿바버샵</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
+          <t>디그헤어 광화문점</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>dighair2@naver.com</t>
+        </is>
+      </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>0507-1380-0857</t>
+          <t>0507-1449-7760</t>
         </is>
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 율곡로14길 55 1층 리얼리굿바버샵</t>
+          <t>서울특별시 종로구 새문안로5길 5 4층</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reallygoodbarbershop</t>
+          <t>https://blog.naver.com/dighair2</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -24811,7 +24815,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -24827,17 +24831,17 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P265" t="n">
+        <v>3663</v>
+      </c>
+      <c r="Q265" t="n">
         <v>205</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
-        <v>205</v>
+        <v>3868</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -24846,12 +24850,12 @@
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>1306555760</t>
+          <t>1114357632</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1306555760</t>
+          <t>https://m.place.naver.com/place/1114357632</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
@@ -24863,29 +24867,25 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>신라이발관</t>
+          <t>보라미용실</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>webomnal@naver.com</t>
+          <t>22jiyeon17@naver.com</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>02-742-0106</t>
-        </is>
-      </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로51나길 3</t>
+          <t>서울특별시 종로구 돈화문로5가길 31</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -24925,13 +24925,13 @@
         </is>
       </c>
       <c r="P266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -24940,12 +24940,12 @@
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>17978876</t>
+          <t>20735567</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17978876</t>
+          <t>https://m.place.naver.com/place/20735567</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
@@ -24957,12 +24957,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>관훈이용원</t>
+          <t>헬로우컷 경희궁자이점</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -24971,12 +24971,12 @@
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로5길 13 삼공빌딩</t>
+          <t>서울특별시 종로구 송월길 99 2101호</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hellocut_gyeonghuigung/</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -25007,17 +25007,17 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P267" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -25026,12 +25026,12 @@
       </c>
       <c r="T267" t="inlineStr">
         <is>
-          <t>1224461666</t>
+          <t>2071321857</t>
         </is>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224461666</t>
+          <t>https://m.place.naver.com/place/2071321857</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
@@ -25043,29 +25043,29 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>호남이발소</t>
+          <t>아우라 J 창신점</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>hiksanin@naver.com</t>
+          <t>a12345asdf@naver.com</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>02-744-9445</t>
+          <t>0507-1440-4533</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로44길 32</t>
+          <t>서울특별시 종로구 창신길 80 1층</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -25105,13 +25105,13 @@
         </is>
       </c>
       <c r="P268" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q268" t="n">
         <v>1</v>
       </c>
       <c r="R268" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -25120,12 +25120,12 @@
       </c>
       <c r="T268" t="inlineStr">
         <is>
-          <t>17978878</t>
+          <t>1120204634</t>
         </is>
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17978878</t>
+          <t>https://m.place.naver.com/place/1120204634</t>
         </is>
       </c>
       <c r="V268" t="inlineStr">
@@ -25137,26 +25137,34 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>세운이발관</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
+          <t>라라헤어</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>henry_0714@naver.com</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0507-1377-3573</t>
+        </is>
+      </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 154-1</t>
+          <t>서울특별시 종로구 종로 19 3층 309-2호</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/henry0714_/</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -25166,7 +25174,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -25187,17 +25195,17 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P269" t="n">
-        <v>1</v>
+        <v>268</v>
       </c>
       <c r="Q269" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R269" t="n">
-        <v>2</v>
+        <v>284</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -25206,12 +25214,12 @@
       </c>
       <c r="T269" t="inlineStr">
         <is>
-          <t>1949417532</t>
+          <t>37798066</t>
         </is>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1949417532</t>
+          <t>https://m.place.naver.com/place/37798066</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
@@ -25223,25 +25231,21 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>동묘이발소</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>h22hyun@naver.com</t>
-        </is>
-      </c>
+          <t>우정헤어샵</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 353-1 2층</t>
+          <t>서울특별시 종로구 진흥로 498</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -25281,13 +25285,13 @@
         </is>
       </c>
       <c r="P270" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q270" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R270" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -25296,12 +25300,12 @@
       </c>
       <c r="T270" t="inlineStr">
         <is>
-          <t>1365205614</t>
+          <t>1382799565</t>
         </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1365205614</t>
+          <t>https://m.place.naver.com/place/1382799565</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
@@ -25313,21 +25317,25 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>신라이발관</t>
+          <t>헤어센스</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>02-730-8983</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 대학로 20</t>
+          <t>서울특별시 종로구 통일로12길 41-1</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -25367,13 +25375,13 @@
         </is>
       </c>
       <c r="P271" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>3</v>
-      </c>
       <c r="R271" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -25382,12 +25390,12 @@
       </c>
       <c r="T271" t="inlineStr">
         <is>
-          <t>1497780078</t>
+          <t>1133200210</t>
         </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1497780078</t>
+          <t>https://m.place.naver.com/place/1133200210</t>
         </is>
       </c>
       <c r="V271" t="inlineStr">
@@ -25399,25 +25407,25 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>대박이발관</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>dlaekdls12@naver.com</t>
-        </is>
-      </c>
+          <t>디앤이헤어</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
-      <c r="E272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>02-6349-0825</t>
+        </is>
+      </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 돈화문로9길 14</t>
+          <t>서울특별시 종로구 통일로 248 2층</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -25457,13 +25465,13 @@
         </is>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q272" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -25472,12 +25480,12 @@
       </c>
       <c r="T272" t="inlineStr">
         <is>
-          <t>1096336202</t>
+          <t>36666954</t>
         </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1096336202</t>
+          <t>https://m.place.naver.com/place/36666954</t>
         </is>
       </c>
       <c r="V272" t="inlineStr">
@@ -25489,25 +25497,25 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>충남이발</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>kim0912s@naver.com</t>
-        </is>
-      </c>
+          <t>까까헤어</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr"/>
-      <c r="E273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>0507-1446-0491</t>
+        </is>
+      </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 평창문화로 45-2</t>
+          <t>서울특별시 종로구 통일로16길 8-3 인왕산아이파크 상가2층</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -25547,13 +25555,13 @@
         </is>
       </c>
       <c r="P273" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -25562,12 +25570,12 @@
       </c>
       <c r="T273" t="inlineStr">
         <is>
-          <t>1671229962</t>
+          <t>31403502</t>
         </is>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1671229962</t>
+          <t>https://m.place.naver.com/place/31403502</t>
         </is>
       </c>
       <c r="V273" t="inlineStr">
@@ -25579,25 +25587,29 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>경진이발</t>
+          <t>린다헤어벨라</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>baegopau10002@naver.com</t>
+          <t>lindayjs@naver.com</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
-      <c r="E274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>02-379-4077</t>
+        </is>
+      </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로41길 38</t>
+          <t>서울특별시 종로구 진흥로 446 로제우스1층</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -25637,13 +25649,13 @@
         </is>
       </c>
       <c r="P274" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q274" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R274" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -25652,12 +25664,12 @@
       </c>
       <c r="T274" t="inlineStr">
         <is>
-          <t>1200956651</t>
+          <t>20334316</t>
         </is>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200956651</t>
+          <t>https://m.place.naver.com/place/20334316</t>
         </is>
       </c>
       <c r="V274" t="inlineStr">
@@ -25669,35 +25681,39 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>파크이발</t>
+          <t>라피오리레헤어 동묘앞역점</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>bbepbird@naver.com</t>
+          <t>yeod81@naver.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
-      <c r="E275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>0507-1332-2363</t>
+        </is>
+      </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로17길 26</t>
+          <t>서울특별시 종로구 종로 347 롯데캐슬천지인상가 2층 6호 라피오리레헤어 동묘역점</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -25723,17 +25739,17 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>2044</v>
       </c>
       <c r="Q275" t="n">
-        <v>4</v>
+        <v>399</v>
       </c>
       <c r="R275" t="n">
-        <v>4</v>
+        <v>2443</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -25742,12 +25758,12 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>19412839</t>
+          <t>1718538119</t>
         </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19412839</t>
+          <t>https://m.place.naver.com/place/1718538119</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
@@ -25759,25 +25775,29 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>신한이발관</t>
+          <t>블루꽃남 동묘역점</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>gyongg99@naver.com</t>
+          <t>a12345asdf@naver.com</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
-      <c r="E276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>02-745-5322</t>
+        </is>
+      </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로20길 39 지하 1 신한이발관</t>
+          <t>서울특별시 종로구 지봉로 62-1</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -25817,13 +25837,13 @@
         </is>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q276" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R276" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -25832,12 +25852,12 @@
       </c>
       <c r="T276" t="inlineStr">
         <is>
-          <t>1777163460</t>
+          <t>20867834</t>
         </is>
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1777163460</t>
+          <t>https://m.place.naver.com/place/20867834</t>
         </is>
       </c>
       <c r="V276" t="inlineStr">
@@ -25849,25 +25869,29 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>하나이발관</t>
+          <t>홍희정프로헤어</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>hyoyeol@naver.com</t>
+          <t>ssa112011@naver.com</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
-      <c r="E277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>02-736-7057</t>
+        </is>
+      </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 수표로 115-1 젬누리빌딩</t>
+          <t>서울특별시 종로구 자하문로 11 2층</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -25907,13 +25931,13 @@
         </is>
       </c>
       <c r="P277" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>1</v>
-      </c>
       <c r="R277" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -25922,12 +25946,12 @@
       </c>
       <c r="T277" t="inlineStr">
         <is>
-          <t>1146095517</t>
+          <t>20928520</t>
         </is>
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1146095517</t>
+          <t>https://m.place.naver.com/place/20928520</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
@@ -25939,25 +25963,29 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>이레이발</t>
+          <t>도니니헤어살롱퀸즈헤나 세검정점</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>choichungue@naver.com</t>
+          <t>caipiroska@naver.com</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
-      <c r="E278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>02-715-9363</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 청계천로 375</t>
+          <t>서울특별시 종로구 자하문로 294 1층</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -25997,13 +26025,13 @@
         </is>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -26012,12 +26040,12 @@
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>1264410216</t>
+          <t>1170672562</t>
         </is>
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264410216</t>
+          <t>https://m.place.naver.com/place/1170672562</t>
         </is>
       </c>
       <c r="V278" t="inlineStr">
@@ -26029,30 +26057,34 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>코리아나호텔바버샵</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr"/>
+          <t>살롱드제이</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>wing3527@naver.com</t>
+        </is>
+      </c>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>0507-1418-2606</t>
+          <t>0507-1481-3398</t>
         </is>
       </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
-          <t>서울특별시 중구 세종대로 135 코리아나호텔 (9층)</t>
+          <t>서울특별시 중구 장충단로 253 헬로 apm. 9층 24호</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>http://www.ceate.kr</t>
+          <t>https://naver.me/GeW57Suq</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -26067,7 +26099,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -26083,17 +26115,17 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P279" t="n">
-        <v>1158</v>
+        <v>259</v>
       </c>
       <c r="Q279" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="R279" t="n">
-        <v>1182</v>
+        <v>264</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -26102,12 +26134,12 @@
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>48188022</t>
+          <t>1568079915</t>
         </is>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/48188022</t>
+          <t>https://m.place.naver.com/place/1568079915</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
@@ -26119,34 +26151,34 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>히든맨즈헤어</t>
+          <t>김희주헤어뱅크</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>oh6274@naver.com</t>
+          <t>sinsoi@naver.com</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>0507-1366-9082</t>
+          <t>02-765-0035</t>
         </is>
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 사직로8길 34 169호,170호 히든맨즈헤어 (서울경찰청정문건너편)</t>
+          <t>서울특별시 종로구 성균관로 19</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mens__director</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -26156,7 +26188,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -26177,17 +26209,17 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P280" t="n">
-        <v>1067</v>
+        <v>183</v>
       </c>
       <c r="Q280" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>1174</v>
+        <v>183</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -26196,12 +26228,12 @@
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>1704281379</t>
+          <t>11696232</t>
         </is>
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1704281379</t>
+          <t>https://m.place.naver.com/place/11696232</t>
         </is>
       </c>
       <c r="V280" t="inlineStr">
@@ -26213,25 +26245,29 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>하나이발관</t>
+          <t>러스헤어</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>hyoyeol@naver.com</t>
+          <t>hsts0830@naver.com</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
-      <c r="E281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>02-743-3578</t>
+        </is>
+      </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 121</t>
+          <t>서울특별시 종로구 혜화동 111-11</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -26271,13 +26307,13 @@
         </is>
       </c>
       <c r="P281" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="Q281" t="n">
         <v>0</v>
       </c>
       <c r="R281" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="S281" t="inlineStr">
         <is>
@@ -26286,12 +26322,12 @@
       </c>
       <c r="T281" t="inlineStr">
         <is>
-          <t>37770420</t>
+          <t>1054039444</t>
         </is>
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37770420</t>
+          <t>https://m.place.naver.com/place/1054039444</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
@@ -26303,25 +26339,29 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>스타이발관</t>
+          <t>YMCA미용실</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>jems80@naver.com</t>
+          <t>wnal13@naver.com</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
-      <c r="E282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>02-732-7580</t>
+        </is>
+      </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로17길 45 경동빌딩 1층</t>
+          <t>서울특별시 종로구 종로 69</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -26361,13 +26401,13 @@
         </is>
       </c>
       <c r="P282" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Q282" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R282" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -26376,12 +26416,12 @@
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>20856131</t>
+          <t>1787058328</t>
         </is>
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20856131</t>
+          <t>https://m.place.naver.com/place/1787058328</t>
         </is>
       </c>
       <c r="V282" t="inlineStr">
@@ -26393,53 +26433,45 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>헤아 포시즌스 호텔점</t>
+          <t>행운미용실</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>wony_91@naver.com</t>
-        </is>
-      </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>info@herrseoul.com</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>0507-1345-5270</t>
-        </is>
-      </c>
+          <t>elfyen@naver.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 97 9층 HERR</t>
+          <t>서울특별시 종로구 종로 368</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>http://www.herrseoul.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -26455,17 +26487,17 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P283" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="Q283" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="R283" t="n">
-        <v>345</v>
+        <v>1</v>
       </c>
       <c r="S283" t="inlineStr">
         <is>
@@ -26474,12 +26506,12 @@
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>36995432</t>
+          <t>1493329258</t>
         </is>
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36995432</t>
+          <t>https://m.place.naver.com/place/1493329258</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
@@ -26491,30 +26523,34 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>태양이발관</t>
+          <t>휴이엠헤어 동묘앞역점</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>yuniworld777@naver.com</t>
+          <t>dongmyomins@naver.com</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>0507-1457-2208</t>
+        </is>
+      </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창신5길 32</t>
+          <t>서울특별시 종로구 종로 336 2층 휴이엠헤어</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/dongmyomins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -26524,12 +26560,12 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -26549,13 +26585,13 @@
         </is>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>2697</v>
       </c>
       <c r="Q284" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="R284" t="n">
-        <v>1</v>
+        <v>2856</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
@@ -26564,12 +26600,12 @@
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>20852275</t>
+          <t>1968485072</t>
         </is>
       </c>
       <c r="U284" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20852275</t>
+          <t>https://m.place.naver.com/place/1968485072</t>
         </is>
       </c>
       <c r="V284" t="inlineStr">
@@ -26581,21 +26617,29 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>삼거리이용원</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr"/>
+          <t>지영헤어</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>imokgi@naver.com</t>
+        </is>
+      </c>
       <c r="D285" t="inlineStr"/>
-      <c r="E285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>02-743-0359</t>
+        </is>
+      </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로 43-4</t>
+          <t>서울특별시 종로구 창신5길 15-3</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -26635,13 +26679,13 @@
         </is>
       </c>
       <c r="P285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q285" t="n">
         <v>0</v>
       </c>
       <c r="R285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S285" t="inlineStr">
         <is>
@@ -26650,12 +26694,12 @@
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>1158410745</t>
+          <t>17979714</t>
         </is>
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1158410745</t>
+          <t>https://m.place.naver.com/place/17979714</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
@@ -26667,30 +26711,30 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>창신이발관</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>chriskang73@naver.com</t>
-        </is>
-      </c>
+          <t>정샘물인스피레이션 에비뉴엘점</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr"/>
-      <c r="E286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>0507-1310-6223</t>
+        </is>
+      </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창신길 96</t>
+          <t>서울특별시 중구 남대문로 73 AVENUEL 10층</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/jungsaemmool_avenuel</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -26700,7 +26744,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -26721,17 +26765,17 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="Q286" t="n">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="R286" t="n">
-        <v>1</v>
+        <v>1627</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -26740,12 +26784,12 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>1960215939</t>
+          <t>36003709</t>
         </is>
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960215939</t>
+          <t>https://m.place.naver.com/place/36003709</t>
         </is>
       </c>
       <c r="V286" t="inlineStr">
@@ -26757,25 +26801,25 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>배관,냉난방공사</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>명진이발</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>a6969235@naver.com</t>
-        </is>
-      </c>
+          <t>관통자들</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr"/>
-      <c r="E287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>0504-1362-7714</t>
+        </is>
+      </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로17길 47</t>
+          <t>서울특별시 종로구 동숭길 64</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -26818,10 +26862,10 @@
         <v>0</v>
       </c>
       <c r="Q287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -26830,12 +26874,12 @@
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>1468446821</t>
+          <t>2016678874</t>
         </is>
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468446821</t>
+          <t>https://m.place.naver.com/place/2016678874</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
@@ -26847,29 +26891,29 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>배관,냉난방공사</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>세화이발관</t>
+          <t>종로구싱크대막힘</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>milk-store@naver.com</t>
+          <t>ybreakiiu18@naver.com</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>02-744-5167</t>
+          <t>0504-1362-6386</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로41길 10</t>
+          <t>서울특별시 종로구 동숭길 64</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -26909,13 +26953,13 @@
         </is>
       </c>
       <c r="P288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q288" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R288" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -26924,12 +26968,12 @@
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>17962656</t>
+          <t>2094230357</t>
         </is>
       </c>
       <c r="U288" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17962656</t>
+          <t>https://m.place.naver.com/place/2094230357</t>
         </is>
       </c>
       <c r="V288" t="inlineStr">
@@ -26946,20 +26990,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>오복이발관</t>
+          <t>우성 이발관</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr"/>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>02-396-7717</t>
-        </is>
-      </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 홍지문길 5</t>
+          <t>서울특별시 종로구 수표로 123-6</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -27002,10 +27042,10 @@
         <v>0</v>
       </c>
       <c r="Q289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S289" t="inlineStr">
         <is>
@@ -27014,12 +27054,12 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>17997158</t>
+          <t>1810176513</t>
         </is>
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17997158</t>
+          <t>https://m.place.naver.com/place/1810176513</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
@@ -27036,24 +27076,20 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>배드바버스굿</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>hyuny___y@naver.com</t>
-        </is>
-      </c>
+          <t>동신이발관</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>0507-1350-7727</t>
+          <t>02-2235-1753</t>
         </is>
       </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로 157 2층 다열274호</t>
+          <t>서울특별시 종로구 지봉로4길 37</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -27093,13 +27129,13 @@
         </is>
       </c>
       <c r="P290" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Q290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R290" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -27108,12 +27144,12 @@
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>1508449173</t>
+          <t>17984510</t>
         </is>
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1508449173</t>
+          <t>https://m.place.naver.com/place/17984510</t>
         </is>
       </c>
       <c r="V290" t="inlineStr">
@@ -27130,29 +27166,29 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>풍년이발관</t>
+          <t>마스터바버샵</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>delpy_s@naver.com</t>
+          <t>charlesbarbershop_th@naver.com</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>02-3675-5359</t>
+          <t>0507-1343-3926</t>
         </is>
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 지봉로 9</t>
+          <t>서울특별시 종로구 인사동5길 29 태화빌딩 지하1층 7호</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/charlesbarbershop_th</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -27162,12 +27198,12 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -27187,13 +27223,13 @@
         </is>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>1544</v>
       </c>
       <c r="Q291" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R291" t="n">
-        <v>1</v>
+        <v>1555</v>
       </c>
       <c r="S291" t="inlineStr">
         <is>
@@ -27202,12 +27238,12 @@
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>20860207</t>
+          <t>17922754</t>
         </is>
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20860207</t>
+          <t>https://m.place.naver.com/place/17922754</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
@@ -27224,25 +27260,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>와코 바버샵</t>
+          <t>참존이발소</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr"/>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>0507-1470-1222</t>
-        </is>
-      </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="inlineStr">
         <is>
-          <t>서울특별시 중구 을지로12길 28 제이메크로타워 111호</t>
+          <t>서울특별시 종로구 종로57길 8</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wackobarbershop_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -27252,7 +27284,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -27273,17 +27305,17 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P292" t="n">
-        <v>584</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="R292" t="n">
-        <v>642</v>
+        <v>1</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -27292,12 +27324,12 @@
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>1928198891</t>
+          <t>1358499310</t>
         </is>
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928198891</t>
+          <t>https://m.place.naver.com/place/1358499310</t>
         </is>
       </c>
       <c r="V292" t="inlineStr">
@@ -27314,16 +27346,24 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>우리이발관</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr"/>
+          <t>미일이발관</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>luvbittt@naver.com</t>
+        </is>
+      </c>
       <c r="D293" t="inlineStr"/>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>02-3673-5113</t>
+        </is>
+      </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로 304</t>
+          <t>서울특별시 종로구 낙산길 5</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -27366,10 +27406,10 @@
         <v>0</v>
       </c>
       <c r="Q293" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R293" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S293" t="inlineStr">
         <is>
@@ -27378,12 +27418,12 @@
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>1444209764</t>
+          <t>17967657</t>
         </is>
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1444209764</t>
+          <t>https://m.place.naver.com/place/17967657</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
@@ -27400,12 +27440,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>낙원이발관</t>
+          <t>클래씨바버샵 센터원점</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>ph_factory@naver.com</t>
+          <t>rudqjasla@naver.com</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -27413,12 +27453,12 @@
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 종로17길 36</t>
+          <t>서울특별시 중구 을지로5길 26 미래에셋센터원 지하1층 105호</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/rudqjasla</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -27428,12 +27468,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -27449,17 +27489,17 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P294" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="Q294" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="R294" t="n">
-        <v>3</v>
+        <v>213</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -27468,12 +27508,12 @@
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>1945146614</t>
+          <t>1061722057</t>
         </is>
       </c>
       <c r="U294" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1945146614</t>
+          <t>https://m.place.naver.com/place/1061722057</t>
         </is>
       </c>
       <c r="V294" t="inlineStr">
@@ -27485,34 +27525,34 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>파스인테리어</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>callajiny@naver.com</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>오클리먼33바버샵 을지로점</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>ocleremon33@gmail.com</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>0507-1472-7457</t>
+          <t>0507-1423-7334</t>
         </is>
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 새문안로2길 10</t>
+          <t>서울특별시 중구 을지로 170 을지트윈타워 B1층 115호</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/ocleremon33</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -27522,7 +27562,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -27543,17 +27583,17 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P295" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="Q295" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R295" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="S295" t="inlineStr">
         <is>
@@ -27562,12 +27602,12 @@
       </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>1507120138</t>
+          <t>2087530432</t>
         </is>
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507120138</t>
+          <t>https://m.place.naver.com/place/2087530432</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
@@ -27579,44 +27619,40 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>오픈빨</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>light74523@naver.com</t>
-        </is>
-      </c>
+          <t>청백이용원</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>0507-1475-0521</t>
+          <t>02-2100-4674</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 창경궁로 109 세운스퀘어, 별관 205호</t>
+          <t>서울특별시 종로구 세종대로 209</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>http://openbal.com</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -27641,13 +27677,13 @@
         </is>
       </c>
       <c r="P296" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>1</v>
-      </c>
       <c r="R296" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -27656,12 +27692,12 @@
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>1887391687</t>
+          <t>1967202167</t>
         </is>
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1887391687</t>
+          <t>https://m.place.naver.com/place/1967202167</t>
         </is>
       </c>
       <c r="V296" t="inlineStr">
@@ -27673,25 +27709,29 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>중장비</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>스카이차사다리차고소작업차업체폐기물처리원상복구철거크레인</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr"/>
+          <t>협동이발소</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>h22hyun@naver.com</t>
+        </is>
+      </c>
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>070-7912-7291</t>
+          <t>0507-1338-2164</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 관수동</t>
+          <t>서울특별시 종로구 종로54길 3 1층</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -27734,10 +27774,10 @@
         <v>0</v>
       </c>
       <c r="Q297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
@@ -27746,12 +27786,12 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>1435541000</t>
+          <t>1149547002</t>
         </is>
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1435541000</t>
+          <t>https://m.place.naver.com/place/1149547002</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
@@ -27763,25 +27803,25 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>중장비</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>스카이차사다리차고소작업차업체폐기물처리원상복구철거크레인</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>장수이용원</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>j_jang_vely@naver.com</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr"/>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>070-7965-7164</t>
-        </is>
-      </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 관훈동</t>
+          <t>서울특별시 종로구 종로17길 36</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -27821,13 +27861,13 @@
         </is>
       </c>
       <c r="P298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q298" t="n">
         <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
@@ -27836,12 +27876,12 @@
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>1749722771</t>
+          <t>20894646</t>
         </is>
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1749722771</t>
+          <t>https://m.place.naver.com/place/20894646</t>
         </is>
       </c>
       <c r="V298" t="inlineStr">
@@ -27853,29 +27893,25 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>중장비</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>스카이차사다리차고소작업차업체폐기물처리원상복구철거크레인</t>
+          <t>피카디리이용원</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>wocns823@naver.com</t>
+          <t>yeonju9195@naver.com</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>070-7970-8644</t>
-        </is>
-      </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="inlineStr">
         <is>
-          <t>서울특별시 종로구 인의동</t>
+          <t>서울특별시 종로구 돈화문로5가길 33</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -27915,30 +27951,4856 @@
         </is>
       </c>
       <c r="P299" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>3</v>
+      </c>
+      <c r="R299" t="n">
+        <v>9</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>19418116</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19418116</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>마제스티바버샵 현대아울렛 동대문점</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>barber_kim@naver.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>0507-1465-2628</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로13길 20 현대시티아울렛 6층</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/barber_kim</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>1081</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>78</v>
+      </c>
+      <c r="R300" t="n">
+        <v>1159</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>638147252</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/638147252</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>고호</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>02-737-2393</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 경희궁1길 32 신문로 하우스 1층 102호</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>428</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>26</v>
+      </c>
+      <c r="R301" t="n">
+        <v>454</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>1111299821</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111299821</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>클래씨바버샵 센트로폴리스점</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>rudqjasla@naver.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>0507-1449-3128</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 우정국로 26 1층 12호</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rudqjasla</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>175</v>
+      </c>
+      <c r="R302" t="n">
+        <v>1175</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>1568475214</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1568475214</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>솔트 더 바버</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>0507-1374-5695</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 계동길 113 1층 1호</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://instagram.com/salt_the_barber</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>6</v>
+      </c>
+      <c r="R303" t="n">
+        <v>42</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>1729274646</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1729274646</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>바버샵 엉클부스 동대문점</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>barberizm@naver.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>02-6327-2727</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 장충단로 247 굿모닝시티 9층 바버샵 엉클부스</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>http://unclebooth.com</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>904</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>80</v>
+      </c>
+      <c r="R304" t="n">
+        <v>984</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>1284597205</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1284597205</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>이마이용원</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>ppassong@naver.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>02-730-9534</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로1길 42</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>1</v>
+      </c>
+      <c r="R305" t="n">
+        <v>22</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>1870076730</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1870076730</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>명성이발</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>jsy34260@naver.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 수표로 112</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>1</v>
+      </c>
+      <c r="R306" t="n">
+        <v>2</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>1188080296</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1188080296</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>바버케이</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>dj_mok@naver.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>02-722-2823</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 20 경희궁파크팰리스 117호</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>62</v>
+      </c>
+      <c r="R307" t="n">
+        <v>207</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>1198195384</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1198195384</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>종묘이발관</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>tisea007@naver.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 146</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
+      <c r="Q308" t="n">
         <v>0</v>
       </c>
-      <c r="R299" t="n">
+      <c r="R308" t="n">
         <v>0</v>
       </c>
-      <c r="S299" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T299" t="inlineStr">
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>1404095890</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1404095890</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>리얼리굿바버샵</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>0507-1380-0857</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 율곡로14길 55 1층 리얼리굿바버샵</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reallygoodbarbershop</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>0</v>
+      </c>
+      <c r="R309" t="n">
+        <v>205</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>1306555760</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1306555760</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>신라이발관</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>webomnal@naver.com</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>02-742-0106</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로51나길 3</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>0</v>
+      </c>
+      <c r="R310" t="n">
+        <v>3</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>17978876</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17978876</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>관훈이용원</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로5길 13 삼공빌딩</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>0</v>
+      </c>
+      <c r="R311" t="n">
+        <v>2</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>1224461666</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1224461666</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>호남이발소</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>hiksanin@naver.com</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>02-744-9445</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로44길 32</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>1</v>
+      </c>
+      <c r="R312" t="n">
+        <v>1</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>17978878</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17978878</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>세운이발관</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 154-1</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>1</v>
+      </c>
+      <c r="R313" t="n">
+        <v>2</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>1949417532</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1949417532</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>동묘이발소</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>h22hyun@naver.com</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 353-1 2층</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>6</v>
+      </c>
+      <c r="R314" t="n">
+        <v>6</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>1365205614</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1365205614</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>신라이발관</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 대학로 20</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>3</v>
+      </c>
+      <c r="R315" t="n">
+        <v>3</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>1497780078</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1497780078</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>대박이발관</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>dlaekdls12@naver.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 돈화문로9길 14</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>3</v>
+      </c>
+      <c r="R316" t="n">
+        <v>3</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>1096336202</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1096336202</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>충남이발</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>kim0912s@naver.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 평창문화로 45-2</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>0</v>
+      </c>
+      <c r="R317" t="n">
+        <v>0</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>1671229962</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1671229962</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>경진이발</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>baegopau10002@naver.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로41길 38</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>2</v>
+      </c>
+      <c r="R318" t="n">
+        <v>2</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>1200956651</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1200956651</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>파크이발</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>bbepbird@naver.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로17길 26</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>4</v>
+      </c>
+      <c r="R319" t="n">
+        <v>4</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>19412839</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19412839</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>신한이발관</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>gyongg99@naver.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 수표로20길 39 지하 1 신한이발관</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>6</v>
+      </c>
+      <c r="R320" t="n">
+        <v>6</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>1777163460</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1777163460</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>하나이발관</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>hyoyeol@naver.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 수표로 115-1 젬누리빌딩</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>1</v>
+      </c>
+      <c r="R321" t="n">
+        <v>1</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>1146095517</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1146095517</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>이레이발</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>choichungue@naver.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 청계천로 375</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>0</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>1264410216</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264410216</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>코리아나호텔바버샵</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>0507-1418-2606</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 세종대로 135 코리아나호텔 (9층)</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>http://www.ceate.kr</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>1158</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>24</v>
+      </c>
+      <c r="R323" t="n">
+        <v>1182</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>48188022</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/48188022</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>히든맨즈헤어</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>oh6274@naver.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>0507-1366-9082</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로8길 34 169호,170호 히든맨즈헤어 (서울경찰청정문건너편)</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mens__director</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>1067</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>107</v>
+      </c>
+      <c r="R324" t="n">
+        <v>1174</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>1704281379</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1704281379</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>하나이발관</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>hyoyeol@naver.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 121</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>7</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>37770420</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37770420</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>스타이발관</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>jems80@naver.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로17길 45 경동빌딩 1층</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>3</v>
+      </c>
+      <c r="R326" t="n">
+        <v>5</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>20856131</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20856131</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>헤아 포시즌스 호텔점</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>wony_91@naver.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>info@herrseoul.com</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0507-1345-5270</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로 97 9층 HERR</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>http://www.herrseoul.com/</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>310</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>35</v>
+      </c>
+      <c r="R327" t="n">
+        <v>345</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>36995432</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36995432</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>태양이발관</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>yuniworld777@naver.com</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 창신5길 32</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>1</v>
+      </c>
+      <c r="R328" t="n">
+        <v>1</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>20852275</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20852275</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>삼거리이용원</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로 43-4</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>0</v>
+      </c>
+      <c r="R329" t="n">
+        <v>1</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>1158410745</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1158410745</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>창신이발관</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>chriskang73@naver.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 창신길 96</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>1</v>
+      </c>
+      <c r="R330" t="n">
+        <v>1</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>1960215939</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1960215939</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>명진이발</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>a6969235@naver.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로17길 47</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>1</v>
+      </c>
+      <c r="R331" t="n">
+        <v>1</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>1468446821</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1468446821</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>세화이발관</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>milk-store@naver.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>02-744-5167</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로41길 10</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>2</v>
+      </c>
+      <c r="R332" t="n">
+        <v>3</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>17962656</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17962656</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>오복이발관</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>02-396-7717</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 홍지문길 5</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>2</v>
+      </c>
+      <c r="R333" t="n">
+        <v>2</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>17997158</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17997158</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>배드바버스굿</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>hyuny___y@naver.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>0507-1350-7727</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로 157 2층 다열274호</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>38</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>1508449173</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1508449173</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>풍년이발관</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>delpy_s@naver.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>02-3675-5359</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 지봉로 9</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>1</v>
+      </c>
+      <c r="R335" t="n">
+        <v>1</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>20860207</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20860207</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>와코 바버샵</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0507-1470-1222</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>서울특별시 중구 을지로12길 28 제이메크로타워 111호</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wackobarbershop_official</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>584</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>58</v>
+      </c>
+      <c r="R336" t="n">
+        <v>642</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>1928198891</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928198891</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>우리이발관</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 304</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>1</v>
+      </c>
+      <c r="R337" t="n">
+        <v>1</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>1444209764</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1444209764</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>낙원이발관</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ph_factory@naver.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로17길 36</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>0</v>
+      </c>
+      <c r="R338" t="n">
+        <v>3</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>1945146614</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1945146614</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>맨레스트</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>majesty7220901@naver.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>0507-1338-0902</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로2길 10 지하2층 맨레스트</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/manrest_rich</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>63</v>
+      </c>
+      <c r="R339" t="n">
+        <v>110</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>1517708008</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1517708008</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>대신이용원</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>cbkb21@naver.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>02-737-7914</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로 11</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>1</v>
+      </c>
+      <c r="R340" t="n">
+        <v>12</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>20863874</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20863874</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>사직이용원</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>ji0408@naver.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>02-735-2339</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로 130 지하1층 14호</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sajik_barbershop_since1986</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>15</v>
+      </c>
+      <c r="R341" t="n">
+        <v>19</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>20840662</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20840662</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>신세계이발관</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>saladin324@naver.com</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 146-1</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>1</v>
+      </c>
+      <c r="R342" t="n">
+        <v>1</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>1466146477</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1466146477</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>클래씨바버샵 르메이에르점</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>rudqjasla@naver.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 19 4층 에스컬레이터 앞</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/classy_barbershop_official?igsh=MXgwM2R6cWt0NjRhYg%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>1320</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>83</v>
+      </c>
+      <c r="R343" t="n">
+        <v>1403</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>1586467823</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1586467823</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>더로드바버샵</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>4el3cp4fr@naver.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0507-1469-1476</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 72-1 태산빌딩 3층 더로드바버샵</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/theroad_gilly/</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>921</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>120</v>
+      </c>
+      <c r="R344" t="n">
+        <v>1041</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>1149180656</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149180656</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>이레이발</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 수표로 115</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>2</v>
+      </c>
+      <c r="R345" t="n">
+        <v>3</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>36005290</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36005290</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>오빠이발</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>jy_yonni@naver.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 종로 354</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>1</v>
+      </c>
+      <c r="R346" t="n">
+        <v>1</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>1430492924</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1430492924</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>종로이발관</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>yesuw21@naver.com</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 사직로1길 58-1 지층</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>0</v>
+      </c>
+      <c r="R347" t="n">
+        <v>0</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>2028449207</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2028449207</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>파스인테리어</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>callajiny@naver.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>0507-1472-7457</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 새문안로2길 10</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>0</v>
+      </c>
+      <c r="R348" t="n">
+        <v>0</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>1507120138</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1507120138</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>오픈빨</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>light74523@naver.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>0507-1475-0521</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 창경궁로 109 세운스퀘어, 별관 205호</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>http://openbal.com</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>1</v>
+      </c>
+      <c r="R349" t="n">
+        <v>1</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>1887391687</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1887391687</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>중장비</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>스카이차사다리차고소작업차업체폐기물처리원상복구철거크레인</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>070-7912-7291</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 관수동</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>1435541000</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1435541000</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>중장비</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>스카이차사다리차고소작업차업체폐기물처리원상복구철거크레인</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>070-7965-7164</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 관훈동</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>1749722771</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1749722771</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>중장비</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>스카이차사다리차고소작업차업체폐기물처리원상복구철거크레인</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>wocns823@naver.com</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>070-7970-8644</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>서울특별시 종로구 인의동</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>0</v>
+      </c>
+      <c r="R352" t="n">
+        <v>0</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
         <is>
           <t>38650432</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="U352" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/38650432</t>
         </is>
       </c>
-      <c r="V299" t="inlineStr">
+      <c r="V352" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
